--- a/MS Excel Crash Course/Lecture 12.xlsx
+++ b/MS Excel Crash Course/Lecture 12.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AR Boot Camp 2k26\MS Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AR Boot Camp 2k26\MS Excel Crash Course\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CD1E61-162F-4501-94FD-FEA207F8D8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB99CB9-35B6-4BF3-915A-58A9B991C2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -191,14 +191,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -212,9 +209,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -222,6 +216,13 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -503,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -511,181 +512,197 @@
     <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>1</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>2</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>3</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>4</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>5</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>6</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>7</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>7</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>8</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>9</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>10</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>10</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C16" s="8" t="s">
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C16" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="8"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="13">
+      <c r="D16" s="13"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="11">
         <v>0.86470000000000002</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="13">
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
         <v>0.52</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="13">
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
         <v>0.49990000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="11">
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
     </row>
   </sheetData>
@@ -694,5 +711,6 @@
     <mergeCell ref="C16:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>